--- a/fixture_8va.xlsx
+++ b/fixture_8va.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\CopaApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F2DBAAF-F80A-4372-BE67-571182374343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB18332-8B17-4312-838F-98C8C2BCF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,6 +232,7 @@
       <b/>
       <sz val="11"/>
       <name val="Palatino Linotype"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -311,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -327,9 +328,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -338,6 +336,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,15 +657,15 @@
     <col min="2" max="2" width="6.44140625" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="35.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -667,15 +674,15 @@
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="3">
@@ -687,15 +694,15 @@
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="3">
@@ -707,15 +714,15 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
       <c r="B4" s="3">
@@ -727,15 +734,15 @@
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="3">
@@ -747,15 +754,15 @@
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="3">
@@ -767,15 +774,15 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>1</v>
       </c>
       <c r="B7" s="3">
@@ -787,15 +794,15 @@
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="3">
@@ -807,15 +814,15 @@
       <c r="D8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>1</v>
       </c>
       <c r="B9" s="3">
@@ -827,15 +834,15 @@
       <c r="D9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>1</v>
       </c>
       <c r="B10" s="3">
@@ -847,15 +854,15 @@
       <c r="D10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>1</v>
       </c>
       <c r="B11" s="3">
@@ -867,15 +874,15 @@
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>1</v>
       </c>
       <c r="B12" s="3">
@@ -887,15 +894,15 @@
       <c r="D12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>1</v>
       </c>
       <c r="B13" s="3">
@@ -907,15 +914,15 @@
       <c r="D13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>1</v>
       </c>
       <c r="B14" s="3">
@@ -927,15 +934,15 @@
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>1</v>
       </c>
       <c r="B15" s="3">
@@ -947,15 +954,15 @@
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
       <c r="B16" s="3">
@@ -967,15 +974,15 @@
       <c r="D16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>2</v>
       </c>
       <c r="B17" s="3">
@@ -987,15 +994,15 @@
       <c r="D17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>2</v>
       </c>
       <c r="B18" s="3">
@@ -1007,15 +1014,15 @@
       <c r="D18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>2</v>
       </c>
       <c r="B19" s="3">
@@ -1027,15 +1034,15 @@
       <c r="D19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>2</v>
       </c>
       <c r="B20" s="3">
@@ -1047,15 +1054,15 @@
       <c r="D20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>2</v>
       </c>
       <c r="B21" s="3">
@@ -1067,15 +1074,15 @@
       <c r="D21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>2</v>
       </c>
       <c r="B22" s="3">
@@ -1087,15 +1094,15 @@
       <c r="D22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>2</v>
       </c>
       <c r="B23" s="3">
@@ -1107,15 +1114,15 @@
       <c r="D23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>2</v>
       </c>
       <c r="B24" s="3">
@@ -1127,15 +1134,15 @@
       <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>2</v>
       </c>
       <c r="B25" s="3">
@@ -1147,15 +1154,15 @@
       <c r="D25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>2</v>
       </c>
       <c r="B26" s="3">
@@ -1167,15 +1174,15 @@
       <c r="D26" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>2</v>
       </c>
       <c r="B27" s="3">
@@ -1187,15 +1194,15 @@
       <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>2</v>
       </c>
       <c r="B28" s="3">
@@ -1207,15 +1214,15 @@
       <c r="D28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>2</v>
       </c>
       <c r="B29" s="3">
@@ -1227,15 +1234,15 @@
       <c r="D29" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>2</v>
       </c>
       <c r="B30" s="3">
@@ -1247,15 +1254,15 @@
       <c r="D30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>2</v>
       </c>
       <c r="B31" s="3">
@@ -1267,15 +1274,15 @@
       <c r="D31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>3</v>
       </c>
       <c r="B32" s="3">
@@ -1287,15 +1294,15 @@
       <c r="D32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>3</v>
       </c>
       <c r="B33" s="3">
@@ -1307,15 +1314,15 @@
       <c r="D33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="5">
         <v>3</v>
       </c>
       <c r="B34" s="3">
@@ -1327,15 +1334,15 @@
       <c r="D34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>3</v>
       </c>
       <c r="B35" s="3">
@@ -1347,15 +1354,15 @@
       <c r="D35" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>3</v>
       </c>
       <c r="B36" s="3">
@@ -1367,15 +1374,15 @@
       <c r="D36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>3</v>
       </c>
       <c r="B37" s="3">
@@ -1387,15 +1394,15 @@
       <c r="D37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>3</v>
       </c>
       <c r="B38" s="3">
@@ -1407,15 +1414,15 @@
       <c r="D38" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>3</v>
       </c>
       <c r="B39" s="3">
@@ -1427,15 +1434,15 @@
       <c r="D39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="5">
         <v>3</v>
       </c>
       <c r="B40" s="3">
@@ -1447,15 +1454,15 @@
       <c r="D40" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="5">
         <v>3</v>
       </c>
       <c r="B41" s="3">
@@ -1467,15 +1474,15 @@
       <c r="D41" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="5">
         <v>3</v>
       </c>
       <c r="B42" s="3">
@@ -1487,15 +1494,15 @@
       <c r="D42" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="5">
         <v>3</v>
       </c>
       <c r="B43" s="3">
@@ -1507,15 +1514,15 @@
       <c r="D43" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>3</v>
       </c>
       <c r="B44" s="3">
@@ -1527,15 +1534,15 @@
       <c r="D44" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="5">
         <v>3</v>
       </c>
       <c r="B45" s="3">
@@ -1547,15 +1554,15 @@
       <c r="D45" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="5">
         <v>3</v>
       </c>
       <c r="B46" s="3">
@@ -1567,15 +1574,15 @@
       <c r="D46" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="5">
         <v>4</v>
       </c>
       <c r="B47" s="3">
@@ -1587,15 +1594,15 @@
       <c r="D47" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="5">
         <v>4</v>
       </c>
       <c r="B48" s="3">
@@ -1607,15 +1614,15 @@
       <c r="D48" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="5">
         <v>4</v>
       </c>
       <c r="B49" s="3">
@@ -1627,15 +1634,15 @@
       <c r="D49" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="5">
         <v>4</v>
       </c>
       <c r="B50" s="3">
@@ -1647,15 +1654,15 @@
       <c r="D50" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="5">
         <v>4</v>
       </c>
       <c r="B51" s="3">
@@ -1667,15 +1674,15 @@
       <c r="D51" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="5">
         <v>4</v>
       </c>
       <c r="B52" s="3">
@@ -1687,15 +1694,15 @@
       <c r="D52" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="5">
         <v>4</v>
       </c>
       <c r="B53" s="3">
@@ -1707,15 +1714,15 @@
       <c r="D53" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="5">
         <v>4</v>
       </c>
       <c r="B54" s="3">
@@ -1727,15 +1734,15 @@
       <c r="D54" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>4</v>
       </c>
       <c r="B55" s="3">
@@ -1747,15 +1754,15 @@
       <c r="D55" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="5">
         <v>4</v>
       </c>
       <c r="B56" s="3">
@@ -1767,15 +1774,15 @@
       <c r="D56" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="5">
         <v>4</v>
       </c>
       <c r="B57" s="3">
@@ -1787,15 +1794,15 @@
       <c r="D57" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="5">
         <v>4</v>
       </c>
       <c r="B58" s="3">
@@ -1807,15 +1814,15 @@
       <c r="D58" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="5">
         <v>4</v>
       </c>
       <c r="B59" s="3">
@@ -1827,15 +1834,15 @@
       <c r="D59" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="5">
         <v>4</v>
       </c>
       <c r="B60" s="3">
@@ -1847,15 +1854,15 @@
       <c r="D60" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="5">
         <v>4</v>
       </c>
       <c r="B61" s="3">
@@ -1867,10 +1874,10 @@
       <c r="D61" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="9" t="s">
         <v>39</v>
       </c>
     </row>
